--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R370"/>
+  <dimension ref="A1:R372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22575,6 +22575,126 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="C371" t="n">
+        <v>317.07</v>
+      </c>
+      <c r="D371" t="n">
+        <v>299.77</v>
+      </c>
+      <c r="E371" t="n">
+        <v>293.83</v>
+      </c>
+      <c r="F371" t="n">
+        <v>297.74</v>
+      </c>
+      <c r="G371" t="n">
+        <v>311.02</v>
+      </c>
+      <c r="H371" t="n">
+        <v>307.51</v>
+      </c>
+      <c r="I371" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="J371" t="n">
+        <v>314.25</v>
+      </c>
+      <c r="K371" t="n">
+        <v>310.57</v>
+      </c>
+      <c r="L371" t="n">
+        <v>306.16</v>
+      </c>
+      <c r="M371" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="N371" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="O371" t="n">
+        <v>331.52</v>
+      </c>
+      <c r="P371" t="n">
+        <v>333.24</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>334.39</v>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="C372" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="D372" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="E372" t="n">
+        <v>291.49</v>
+      </c>
+      <c r="F372" t="n">
+        <v>296.36</v>
+      </c>
+      <c r="G372" t="n">
+        <v>310.39</v>
+      </c>
+      <c r="H372" t="n">
+        <v>306.5</v>
+      </c>
+      <c r="I372" t="n">
+        <v>307.91</v>
+      </c>
+      <c r="J372" t="n">
+        <v>313.57</v>
+      </c>
+      <c r="K372" t="n">
+        <v>309.43</v>
+      </c>
+      <c r="L372" t="n">
+        <v>305.56</v>
+      </c>
+      <c r="M372" t="n">
+        <v>325.28</v>
+      </c>
+      <c r="N372" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="O372" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="P372" t="n">
+        <v>331.09</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>335.44</v>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22586,7 +22706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B393"/>
+  <dimension ref="A1:B395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26519,6 +26639,26 @@
       </c>
       <c r="B393" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -26687,28 +26827,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01736575592333688</v>
+        <v>-0.01622847986685814</v>
       </c>
       <c r="J2" t="n">
+        <v>371</v>
+      </c>
+      <c r="K2" t="n">
         <v>369</v>
       </c>
-      <c r="K2" t="n">
-        <v>367</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001620794150622995</v>
+        <v>0.0001431053193873266</v>
       </c>
       <c r="M2" t="n">
-        <v>7.932481226754204</v>
+        <v>7.894814316588547</v>
       </c>
       <c r="N2" t="n">
-        <v>99.61592125675435</v>
+        <v>99.08383905349179</v>
       </c>
       <c r="O2" t="n">
-        <v>9.980777587781143</v>
+        <v>9.954086550432027</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6395467517433</v>
+        <v>347.6272409132492</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26765,28 +26905,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03443754305084516</v>
+        <v>-0.03407729281263161</v>
       </c>
       <c r="J3" t="n">
+        <v>371</v>
+      </c>
+      <c r="K3" t="n">
         <v>369</v>
       </c>
-      <c r="K3" t="n">
-        <v>367</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.001276361692606476</v>
+        <v>0.00126361017590837</v>
       </c>
       <c r="M3" t="n">
-        <v>5.443573986779318</v>
+        <v>5.416551858713622</v>
       </c>
       <c r="N3" t="n">
-        <v>49.69074556126181</v>
+        <v>49.42344408876617</v>
       </c>
       <c r="O3" t="n">
-        <v>7.049166302568114</v>
+        <v>7.03018094281834</v>
       </c>
       <c r="P3" t="n">
-        <v>317.1230407930906</v>
+        <v>317.1191446485066</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26843,28 +26983,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3001738217563179</v>
+        <v>-0.3020517900034878</v>
       </c>
       <c r="J4" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K4" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04987267915192517</v>
+        <v>0.05098872843856339</v>
       </c>
       <c r="M4" t="n">
-        <v>6.739062044713075</v>
+        <v>6.710708229267147</v>
       </c>
       <c r="N4" t="n">
-        <v>91.03963540701127</v>
+        <v>90.56593822803067</v>
       </c>
       <c r="O4" t="n">
-        <v>9.541469247815625</v>
+        <v>9.516613800508596</v>
       </c>
       <c r="P4" t="n">
-        <v>308.5909713801904</v>
+        <v>308.6114347040426</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26921,28 +27061,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05625931428183627</v>
+        <v>0.04908529576377169</v>
       </c>
       <c r="J5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007748005505540112</v>
+        <v>0.0005956732300985701</v>
       </c>
       <c r="M5" t="n">
-        <v>10.337001227814</v>
+        <v>10.32293999021016</v>
       </c>
       <c r="N5" t="n">
-        <v>222.921549943016</v>
+        <v>221.9844263054534</v>
       </c>
       <c r="O5" t="n">
-        <v>14.93055758982283</v>
+        <v>14.8991417976155</v>
       </c>
       <c r="P5" t="n">
-        <v>298.1404862552253</v>
+        <v>298.2170967766281</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26999,28 +27139,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3717306900918211</v>
+        <v>0.3641744936256611</v>
       </c>
       <c r="J6" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01262959978930178</v>
+        <v>0.01225338324893377</v>
       </c>
       <c r="M6" t="n">
-        <v>15.32342640509789</v>
+        <v>15.28088945262932</v>
       </c>
       <c r="N6" t="n">
-        <v>586.7995077436544</v>
+        <v>583.9136503361394</v>
       </c>
       <c r="O6" t="n">
-        <v>24.22394492529353</v>
+        <v>24.16430529388626</v>
       </c>
       <c r="P6" t="n">
-        <v>294.5373614966006</v>
+        <v>294.6183946716105</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27077,28 +27217,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2691200464321704</v>
+        <v>-0.2750921634379977</v>
       </c>
       <c r="J7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K7" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02103283768297071</v>
+        <v>0.02217394414496421</v>
       </c>
       <c r="M7" t="n">
-        <v>10.26849674695394</v>
+        <v>10.24238609564869</v>
       </c>
       <c r="N7" t="n">
-        <v>178.7837842256883</v>
+        <v>177.9835923009736</v>
       </c>
       <c r="O7" t="n">
-        <v>13.37100535583201</v>
+        <v>13.34104914543731</v>
       </c>
       <c r="P7" t="n">
-        <v>323.468917014764</v>
+        <v>323.5339780643973</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27155,28 +27295,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1936174387235321</v>
+        <v>-0.1998094243862867</v>
       </c>
       <c r="J8" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K8" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01452843730364584</v>
+        <v>0.01560607311997442</v>
       </c>
       <c r="M8" t="n">
-        <v>8.948450424870565</v>
+        <v>8.937512681718887</v>
       </c>
       <c r="N8" t="n">
-        <v>134.8589915378866</v>
+        <v>134.3111599219928</v>
       </c>
       <c r="O8" t="n">
-        <v>11.6128804152065</v>
+        <v>11.58926917117696</v>
       </c>
       <c r="P8" t="n">
-        <v>317.982390954084</v>
+        <v>318.0498483004329</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27233,28 +27373,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2213555587628961</v>
+        <v>-0.2228140119291429</v>
       </c>
       <c r="J9" t="n">
+        <v>371</v>
+      </c>
+      <c r="K9" t="n">
         <v>369</v>
       </c>
-      <c r="K9" t="n">
-        <v>367</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0182643281636351</v>
+        <v>0.01870064950049444</v>
       </c>
       <c r="M9" t="n">
-        <v>8.833646511721817</v>
+        <v>8.794199016202731</v>
       </c>
       <c r="N9" t="n">
-        <v>141.0299532589772</v>
+        <v>140.2797207151184</v>
       </c>
       <c r="O9" t="n">
-        <v>11.87560327979077</v>
+        <v>11.84397402543244</v>
       </c>
       <c r="P9" t="n">
-        <v>315.9942337214813</v>
+        <v>316.0100235492155</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27311,28 +27451,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3580968681682316</v>
+        <v>-0.3508008273463215</v>
       </c>
       <c r="J10" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K10" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06404456098373357</v>
+        <v>0.06211284140189266</v>
       </c>
       <c r="M10" t="n">
-        <v>7.721530610823612</v>
+        <v>7.70898669504781</v>
       </c>
       <c r="N10" t="n">
-        <v>99.38932435145588</v>
+        <v>99.10493584490379</v>
       </c>
       <c r="O10" t="n">
-        <v>9.969419459098704</v>
+        <v>9.955146199072306</v>
       </c>
       <c r="P10" t="n">
-        <v>316.4567518515101</v>
+        <v>316.3772718882714</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27389,28 +27529,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1934050731748824</v>
+        <v>-0.1919753743988591</v>
       </c>
       <c r="J11" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K11" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01341186834992902</v>
+        <v>0.01336097616179621</v>
       </c>
       <c r="M11" t="n">
-        <v>9.485190524504871</v>
+        <v>9.439179183800293</v>
       </c>
       <c r="N11" t="n">
-        <v>145.9311825651866</v>
+        <v>145.149659107972</v>
       </c>
       <c r="O11" t="n">
-        <v>12.08019795223516</v>
+        <v>12.04780723235444</v>
       </c>
       <c r="P11" t="n">
-        <v>313.7533105760044</v>
+        <v>313.7377389545719</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27467,28 +27607,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2186192819568124</v>
+        <v>-0.2175899205796439</v>
       </c>
       <c r="J12" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K12" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01129435729713657</v>
+        <v>0.01131225504571776</v>
       </c>
       <c r="M12" t="n">
-        <v>10.95262010811919</v>
+        <v>10.89717515401221</v>
       </c>
       <c r="N12" t="n">
-        <v>221.8953445150027</v>
+        <v>220.6949442010893</v>
       </c>
       <c r="O12" t="n">
-        <v>14.8961520036217</v>
+        <v>14.85580506741689</v>
       </c>
       <c r="P12" t="n">
-        <v>310.6570579004589</v>
+        <v>310.6458458971004</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27545,28 +27685,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2215943235097542</v>
+        <v>-0.2104415423273762</v>
       </c>
       <c r="J13" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K13" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009434086100713834</v>
+        <v>0.008591458751092684</v>
       </c>
       <c r="M13" t="n">
-        <v>12.43811236450361</v>
+        <v>12.41278447182901</v>
       </c>
       <c r="N13" t="n">
-        <v>273.4428546903637</v>
+        <v>272.5546356966167</v>
       </c>
       <c r="O13" t="n">
-        <v>16.53610760397875</v>
+        <v>16.50922880381203</v>
       </c>
       <c r="P13" t="n">
-        <v>321.1245901595573</v>
+        <v>321.0030967428908</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27623,28 +27763,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05091123861545117</v>
+        <v>0.05254973382645412</v>
       </c>
       <c r="J14" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K14" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001092277498317196</v>
+        <v>0.001176423356858747</v>
       </c>
       <c r="M14" t="n">
-        <v>8.430857311626625</v>
+        <v>8.390451221265488</v>
       </c>
       <c r="N14" t="n">
-        <v>126.1380146910664</v>
+        <v>125.462937437088</v>
       </c>
       <c r="O14" t="n">
-        <v>11.23111814073142</v>
+        <v>11.20102394592066</v>
       </c>
       <c r="P14" t="n">
-        <v>327.7180952403621</v>
+        <v>327.7002646962057</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27701,28 +27841,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2653674798141287</v>
+        <v>0.2637652250845917</v>
       </c>
       <c r="J15" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K15" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03478947440346669</v>
+        <v>0.03474930964725154</v>
       </c>
       <c r="M15" t="n">
-        <v>7.83029611240142</v>
+        <v>7.797715639228953</v>
       </c>
       <c r="N15" t="n">
-        <v>103.8954166495454</v>
+        <v>103.3454715931981</v>
       </c>
       <c r="O15" t="n">
-        <v>10.19291011681872</v>
+        <v>10.16589748095062</v>
       </c>
       <c r="P15" t="n">
-        <v>325.1830550860178</v>
+        <v>325.2004903761012</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27779,28 +27919,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1931323116923526</v>
+        <v>0.1909322577815699</v>
       </c>
       <c r="J16" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K16" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01591214377831818</v>
+        <v>0.01572443724870609</v>
       </c>
       <c r="M16" t="n">
-        <v>8.563225129342637</v>
+        <v>8.527899807050586</v>
       </c>
       <c r="N16" t="n">
-        <v>121.0450275946746</v>
+        <v>120.4127458095083</v>
       </c>
       <c r="O16" t="n">
-        <v>11.0020465184744</v>
+        <v>10.97327416086504</v>
       </c>
       <c r="P16" t="n">
-        <v>329.127108687566</v>
+        <v>329.1512779449728</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27857,28 +27997,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1160954264874132</v>
+        <v>0.1110465167009153</v>
       </c>
       <c r="J17" t="n">
+        <v>371</v>
+      </c>
+      <c r="K17" t="n">
         <v>369</v>
       </c>
-      <c r="K17" t="n">
-        <v>367</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.005709754868544081</v>
+        <v>0.005278412096190177</v>
       </c>
       <c r="M17" t="n">
-        <v>8.789583334273354</v>
+        <v>8.767558378648733</v>
       </c>
       <c r="N17" t="n">
-        <v>126.929386008349</v>
+        <v>126.3688427063308</v>
       </c>
       <c r="O17" t="n">
-        <v>11.26629424470837</v>
+        <v>11.24138971419151</v>
       </c>
       <c r="P17" t="n">
-        <v>336.7108142009845</v>
+        <v>336.7651509311382</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27916,7 +28056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R370"/>
+  <dimension ref="A1:R372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61783,6 +61923,190 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-38.22454331710243,174.71326160719724</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-38.22391503954471,174.71381507406397</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-38.22325952131251,174.71420737959517</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-38.22258255737152,174.71447281352314</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-38.2218869979583,174.71462824273144</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-38.22111963377006,174.71469028416956</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-38.22035472792776,174.71469483413534</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-38.219646640734446,174.71461218433046</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-38.21894560642138,174.71450078639916</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-38.21823877825808,174.71448424017203</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-38.21752425556264,174.71447532813238</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-38.21683279992712,174.71415820735336</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-38.216134622150804,174.71400723517579</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-38.21543343021755,174.71390522649347</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>-38.214733639196744,174.7137884793869</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-38.21403322416996,174.7136781948588</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-38.22454533650201,174.71327355722687</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-38.22391696453434,174.71382646559326</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-38.223262842811394,174.7142270354025</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-38.22258697341514,174.71449894657894</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-38.22188960228386,174.71464365438803</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-38.221120081564,174.71469745702964</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-38.22035413360931,174.71470634468506</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-38.21964546663962,174.7146314281149</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-38.21894513401225,174.7145085293871</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-38.2182379862797,174.71449722093817</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-38.21752375432494,174.71448215093002</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-38.21683166759737,174.71417068755545</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>-38.21613357178363,174.71401823258208</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-38.21543160021021,174.71392438674172</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>-38.21473131110176,174.71381285462118</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>-38.21403436113494,174.71366629078622</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R372"/>
+  <dimension ref="A1:R374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22695,6 +22695,126 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="C373" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="D373" t="n">
+        <v>298.16</v>
+      </c>
+      <c r="E373" t="n">
+        <v>292.08</v>
+      </c>
+      <c r="F373" t="n">
+        <v>297.81</v>
+      </c>
+      <c r="G373" t="n">
+        <v>311.57</v>
+      </c>
+      <c r="H373" t="n">
+        <v>307.43</v>
+      </c>
+      <c r="I373" t="n">
+        <v>308.38</v>
+      </c>
+      <c r="J373" t="n">
+        <v>313.34</v>
+      </c>
+      <c r="K373" t="n">
+        <v>308.03</v>
+      </c>
+      <c r="L373" t="n">
+        <v>303.32</v>
+      </c>
+      <c r="M373" t="n">
+        <v>324.69</v>
+      </c>
+      <c r="N373" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="O373" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="P373" t="n">
+        <v>331.09</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>335.44</v>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="C374" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="D374" t="n">
+        <v>298.48</v>
+      </c>
+      <c r="E374" t="n">
+        <v>292.46</v>
+      </c>
+      <c r="F374" t="n">
+        <v>296.97</v>
+      </c>
+      <c r="G374" t="n">
+        <v>310.75</v>
+      </c>
+      <c r="H374" t="n">
+        <v>308.38</v>
+      </c>
+      <c r="I374" t="n">
+        <v>308.57</v>
+      </c>
+      <c r="J374" t="n">
+        <v>312.82</v>
+      </c>
+      <c r="K374" t="n">
+        <v>307.41</v>
+      </c>
+      <c r="L374" t="n">
+        <v>302.32</v>
+      </c>
+      <c r="M374" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="N374" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="O374" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="P374" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>340.32</v>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22706,7 +22826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B395"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26659,6 +26779,26 @@
       </c>
       <c r="B395" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -26827,28 +26967,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01622847986685814</v>
+        <v>-0.01659466441672098</v>
       </c>
       <c r="J2" t="n">
+        <v>373</v>
+      </c>
+      <c r="K2" t="n">
         <v>371</v>
       </c>
-      <c r="K2" t="n">
-        <v>369</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001431053193873266</v>
+        <v>0.0001512711029706404</v>
       </c>
       <c r="M2" t="n">
-        <v>7.894814316588547</v>
+        <v>7.855246761023434</v>
       </c>
       <c r="N2" t="n">
-        <v>99.08383905349179</v>
+        <v>98.5518518989529</v>
       </c>
       <c r="O2" t="n">
-        <v>9.954086550432027</v>
+        <v>9.927328537877292</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6272409132492</v>
+        <v>347.6312081277977</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26905,28 +27045,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03407729281263161</v>
+        <v>-0.03444904995093746</v>
       </c>
       <c r="J3" t="n">
+        <v>373</v>
+      </c>
+      <c r="K3" t="n">
         <v>371</v>
       </c>
-      <c r="K3" t="n">
-        <v>369</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00126361017590837</v>
+        <v>0.001305404832597779</v>
       </c>
       <c r="M3" t="n">
-        <v>5.416551858713622</v>
+        <v>5.389525113532762</v>
       </c>
       <c r="N3" t="n">
-        <v>49.42344408876617</v>
+        <v>49.15769350400688</v>
       </c>
       <c r="O3" t="n">
-        <v>7.03018094281834</v>
+        <v>7.011254773862299</v>
       </c>
       <c r="P3" t="n">
-        <v>317.1191446485066</v>
+        <v>317.1231782703896</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26983,28 +27123,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3020517900034878</v>
+        <v>-0.304449416613717</v>
       </c>
       <c r="J4" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05098872843856339</v>
+        <v>0.05228348835142071</v>
       </c>
       <c r="M4" t="n">
-        <v>6.710708229267147</v>
+        <v>6.684945851245915</v>
       </c>
       <c r="N4" t="n">
-        <v>90.56593822803067</v>
+        <v>90.10457463017218</v>
       </c>
       <c r="O4" t="n">
-        <v>9.516613800508596</v>
+        <v>9.492342947353524</v>
       </c>
       <c r="P4" t="n">
-        <v>308.6114347040426</v>
+        <v>308.6376170006642</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27061,28 +27201,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04908529576377169</v>
+        <v>0.04170364200747078</v>
       </c>
       <c r="J5" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K5" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005956732300985701</v>
+        <v>0.0004341800057148237</v>
       </c>
       <c r="M5" t="n">
-        <v>10.32293999021016</v>
+        <v>10.31018026886223</v>
       </c>
       <c r="N5" t="n">
-        <v>221.9844263054534</v>
+        <v>221.0713858565488</v>
       </c>
       <c r="O5" t="n">
-        <v>14.8991417976155</v>
+        <v>14.86846951964286</v>
       </c>
       <c r="P5" t="n">
-        <v>298.2170967766281</v>
+        <v>298.2961163198068</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27139,28 +27279,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3641744936256611</v>
+        <v>0.3571488963376224</v>
       </c>
       <c r="J6" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K6" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01225338324893377</v>
+        <v>0.01191233704349925</v>
       </c>
       <c r="M6" t="n">
-        <v>15.28088945262932</v>
+        <v>15.23576832349191</v>
       </c>
       <c r="N6" t="n">
-        <v>583.9136503361394</v>
+        <v>581.0244376388433</v>
       </c>
       <c r="O6" t="n">
-        <v>24.16430529388626</v>
+        <v>24.10444850310505</v>
       </c>
       <c r="P6" t="n">
-        <v>294.6183946716105</v>
+        <v>294.6939299439161</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27217,28 +27357,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2750921634379977</v>
+        <v>-0.2804132687695609</v>
       </c>
       <c r="J7" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K7" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02217394414496421</v>
+        <v>0.02324966783776206</v>
       </c>
       <c r="M7" t="n">
-        <v>10.24238609564869</v>
+        <v>10.2131974916615</v>
       </c>
       <c r="N7" t="n">
-        <v>177.9835923009736</v>
+        <v>177.1603754966735</v>
       </c>
       <c r="O7" t="n">
-        <v>13.34104914543731</v>
+        <v>13.31016061122755</v>
       </c>
       <c r="P7" t="n">
-        <v>323.5339780643973</v>
+        <v>323.5920938259948</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27295,28 +27435,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1998094243862867</v>
+        <v>-0.2048790458369968</v>
       </c>
       <c r="J8" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K8" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01560607311997442</v>
+        <v>0.01655684070960106</v>
       </c>
       <c r="M8" t="n">
-        <v>8.937512681718887</v>
+        <v>8.919930087293006</v>
       </c>
       <c r="N8" t="n">
-        <v>134.3111599219928</v>
+        <v>133.71173869975</v>
       </c>
       <c r="O8" t="n">
-        <v>11.58926917117696</v>
+        <v>11.56337920764298</v>
       </c>
       <c r="P8" t="n">
-        <v>318.0498483004329</v>
+        <v>318.1052075596544</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27373,28 +27513,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2228140119291429</v>
+        <v>-0.2245088667910747</v>
       </c>
       <c r="J9" t="n">
+        <v>373</v>
+      </c>
+      <c r="K9" t="n">
         <v>371</v>
       </c>
-      <c r="K9" t="n">
-        <v>369</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01870064950049444</v>
+        <v>0.01918283747933924</v>
       </c>
       <c r="M9" t="n">
-        <v>8.794199016202731</v>
+        <v>8.756494492549011</v>
       </c>
       <c r="N9" t="n">
-        <v>140.2797207151184</v>
+        <v>139.5377514230362</v>
       </c>
       <c r="O9" t="n">
-        <v>11.84397402543244</v>
+        <v>11.81260984808337</v>
       </c>
       <c r="P9" t="n">
-        <v>316.0100235492155</v>
+        <v>316.028411945678</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27451,28 +27591,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3508008273463215</v>
+        <v>-0.3445524088652727</v>
       </c>
       <c r="J10" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K10" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06211284140189266</v>
+        <v>0.06056204044086178</v>
       </c>
       <c r="M10" t="n">
-        <v>7.70898669504781</v>
+        <v>7.692426307459331</v>
       </c>
       <c r="N10" t="n">
-        <v>99.10493584490379</v>
+        <v>98.75994603293999</v>
       </c>
       <c r="O10" t="n">
-        <v>9.955146199072306</v>
+        <v>9.937803883803504</v>
       </c>
       <c r="P10" t="n">
-        <v>316.3772718882714</v>
+        <v>316.3090365534559</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27529,28 +27669,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1919753743988591</v>
+        <v>-0.1929518976521025</v>
       </c>
       <c r="J11" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K11" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01336097616179621</v>
+        <v>0.01364137083469497</v>
       </c>
       <c r="M11" t="n">
-        <v>9.439179183800293</v>
+        <v>9.394360657805789</v>
       </c>
       <c r="N11" t="n">
-        <v>145.149659107972</v>
+        <v>144.3702134609231</v>
       </c>
       <c r="O11" t="n">
-        <v>12.04780723235444</v>
+        <v>12.01541565909907</v>
       </c>
       <c r="P11" t="n">
-        <v>313.7377389545719</v>
+        <v>313.7484069418372</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27607,28 +27747,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2175899205796439</v>
+        <v>-0.2197471417758078</v>
       </c>
       <c r="J12" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K12" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01131225504571776</v>
+        <v>0.01165923099401889</v>
       </c>
       <c r="M12" t="n">
-        <v>10.89717515401221</v>
+        <v>10.85178574152492</v>
       </c>
       <c r="N12" t="n">
-        <v>220.6949442010893</v>
+        <v>219.5259831185376</v>
       </c>
       <c r="O12" t="n">
-        <v>14.85580506741689</v>
+        <v>14.81640925185781</v>
       </c>
       <c r="P12" t="n">
-        <v>310.6458458971004</v>
+        <v>310.6694103057783</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27685,28 +27825,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2104415423273762</v>
+        <v>-0.2012151484900856</v>
       </c>
       <c r="J13" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K13" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008591458751092684</v>
+        <v>0.007934122117834175</v>
       </c>
       <c r="M13" t="n">
-        <v>12.41278447182901</v>
+        <v>12.38049004155542</v>
       </c>
       <c r="N13" t="n">
-        <v>272.5546356966167</v>
+        <v>271.4973755670571</v>
       </c>
       <c r="O13" t="n">
-        <v>16.50922880381203</v>
+        <v>16.47717741505071</v>
       </c>
       <c r="P13" t="n">
-        <v>321.0030967428908</v>
+        <v>320.9023411601555</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27763,28 +27903,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05254973382645412</v>
+        <v>0.05258031986615908</v>
       </c>
       <c r="J14" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K14" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001176423356858747</v>
+        <v>0.001190714961849304</v>
       </c>
       <c r="M14" t="n">
-        <v>8.390451221265488</v>
+        <v>8.347102338666589</v>
       </c>
       <c r="N14" t="n">
-        <v>125.462937437088</v>
+        <v>124.7820554150026</v>
       </c>
       <c r="O14" t="n">
-        <v>11.20102394592066</v>
+        <v>11.17058885712846</v>
       </c>
       <c r="P14" t="n">
-        <v>327.7002646962057</v>
+        <v>327.6999358435943</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27841,28 +27981,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2637652250845917</v>
+        <v>0.2606134553519311</v>
       </c>
       <c r="J15" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K15" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03474930964725154</v>
+        <v>0.03429635221876537</v>
       </c>
       <c r="M15" t="n">
-        <v>7.797715639228953</v>
+        <v>7.775107840204655</v>
       </c>
       <c r="N15" t="n">
-        <v>103.3454715931981</v>
+        <v>102.8362445543126</v>
       </c>
       <c r="O15" t="n">
-        <v>10.16589748095062</v>
+        <v>10.14082070417935</v>
       </c>
       <c r="P15" t="n">
-        <v>325.2004903761012</v>
+        <v>325.234870540516</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27919,28 +28059,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1909322577815699</v>
+        <v>0.1869558900672928</v>
       </c>
       <c r="J16" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K16" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01572443724870609</v>
+        <v>0.015240175281376</v>
       </c>
       <c r="M16" t="n">
-        <v>8.527899807050586</v>
+        <v>8.502071284105323</v>
       </c>
       <c r="N16" t="n">
-        <v>120.4127458095083</v>
+        <v>119.8366966878405</v>
       </c>
       <c r="O16" t="n">
-        <v>10.97327416086504</v>
+        <v>10.94699487018426</v>
       </c>
       <c r="P16" t="n">
-        <v>329.1512779449728</v>
+        <v>329.1950655511783</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27997,28 +28137,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1110465167009153</v>
+        <v>0.1091800327754759</v>
       </c>
       <c r="J17" t="n">
+        <v>373</v>
+      </c>
+      <c r="K17" t="n">
         <v>371</v>
       </c>
-      <c r="K17" t="n">
-        <v>369</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.005278412096190177</v>
+        <v>0.005156612623348766</v>
       </c>
       <c r="M17" t="n">
-        <v>8.767558378648733</v>
+        <v>8.73315824457339</v>
       </c>
       <c r="N17" t="n">
-        <v>126.3688427063308</v>
+        <v>125.7371823971255</v>
       </c>
       <c r="O17" t="n">
-        <v>11.24138971419151</v>
+        <v>11.21325922277397</v>
       </c>
       <c r="P17" t="n">
-        <v>336.7651509311382</v>
+        <v>336.7852625539325</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28056,7 +28196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R372"/>
+  <dimension ref="A1:R374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62107,6 +62247,190 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-38.2245479975781,174.71328930446313</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-38.22391732311072,174.71382858754484</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-38.22326255972922,174.7142253601916</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-38.222585859968795,174.71449235747485</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-38.22188686585478,174.71462746098075</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-38.22111924283847,174.71468402214887</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-38.22035468085307,174.71469574586203</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-38.219645793163366,174.71462607629329</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-38.21894497422671,174.71451114833891</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-38.21823701367273,174.71451316222945</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-38.217521883034024,174.71450762270692</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-38.216831060256325,174.71417738148187</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>-38.21613293290002,174.71402492172595</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-38.21543160021021,174.71392438674172</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>-38.21473131110176,174.71381285462118</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>-38.21403436113494,174.71366629078622</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-38.2245460159259,174.71327757779773</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-38.22391732311072,174.71382858754484</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-38.22326195582053,174.71422178640836</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-38.22258514283366,174.7144881136452</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-38.22188845109674,174.71463684198895</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-38.2211198256818,174.71469335825245</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-38.22035523986455,174.71468491910716</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-38.21964592516224,174.71462391279087</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-38.218944612972194,174.71451706944723</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-38.21823658294608,174.71452022194399</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-38.217521047634506,174.71451899403536</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-38.21683019556672,174.71418691181756</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>-38.21613202330236,174.7140344452526</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-38.21543016002473,174.7139394655162</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>-38.21472988175724,174.71382781988044</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>-38.21403964529934,174.71361096518618</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R374"/>
+  <dimension ref="A1:R375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22815,6 +22815,66 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="C375" t="n">
+        <v>316.18</v>
+      </c>
+      <c r="D375" t="n">
+        <v>298.64</v>
+      </c>
+      <c r="E375" t="n">
+        <v>293.36</v>
+      </c>
+      <c r="F375" t="n">
+        <v>298.78</v>
+      </c>
+      <c r="G375" t="n">
+        <v>313.76</v>
+      </c>
+      <c r="H375" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="I375" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="J375" t="n">
+        <v>311.19</v>
+      </c>
+      <c r="K375" t="n">
+        <v>305.26</v>
+      </c>
+      <c r="L375" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="M375" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="N375" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="O375" t="n">
+        <v>331.94</v>
+      </c>
+      <c r="P375" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>344.08</v>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22826,7 +22886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26799,6 +26859,16 @@
       </c>
       <c r="B397" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -26967,28 +27037,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01659466441672098</v>
+        <v>-0.01863362781693485</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001512711029706404</v>
+        <v>0.0001916865553237557</v>
       </c>
       <c r="M2" t="n">
-        <v>7.855246761023434</v>
+        <v>7.845740166348289</v>
       </c>
       <c r="N2" t="n">
-        <v>98.5518518989529</v>
+        <v>98.328055322431</v>
       </c>
       <c r="O2" t="n">
-        <v>9.927328537877292</v>
+        <v>9.916050389264417</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6312081277977</v>
+        <v>347.6534418446271</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27045,28 +27115,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03444904995093746</v>
+        <v>-0.03446549800370446</v>
       </c>
       <c r="J3" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K3" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001305404832597779</v>
+        <v>0.001313811911151541</v>
       </c>
       <c r="M3" t="n">
-        <v>5.389525113532762</v>
+        <v>5.375131994746155</v>
       </c>
       <c r="N3" t="n">
-        <v>49.15769350400688</v>
+        <v>49.0255518429943</v>
       </c>
       <c r="O3" t="n">
-        <v>7.011254773862299</v>
+        <v>7.001824893768359</v>
       </c>
       <c r="P3" t="n">
-        <v>317.1231782703896</v>
+        <v>317.1233576268938</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27123,28 +27193,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.304449416613717</v>
+        <v>-0.3054481021089648</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05228348835142071</v>
+        <v>0.05287817960968821</v>
       </c>
       <c r="M4" t="n">
-        <v>6.684945851245915</v>
+        <v>6.671368281653401</v>
       </c>
       <c r="N4" t="n">
-        <v>90.10457463017218</v>
+        <v>89.8714373662806</v>
       </c>
       <c r="O4" t="n">
-        <v>9.492342947353524</v>
+        <v>9.480054713253537</v>
       </c>
       <c r="P4" t="n">
-        <v>308.6376170006642</v>
+        <v>308.6485775810184</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27201,28 +27271,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04170364200747078</v>
+        <v>0.03861797079599187</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004341800057148237</v>
+        <v>0.0003741902924568885</v>
       </c>
       <c r="M5" t="n">
-        <v>10.31018026886223</v>
+        <v>10.30016990422981</v>
       </c>
       <c r="N5" t="n">
-        <v>221.0713858565488</v>
+        <v>220.5771745292095</v>
       </c>
       <c r="O5" t="n">
-        <v>14.86846951964286</v>
+        <v>14.85184077914955</v>
       </c>
       <c r="P5" t="n">
-        <v>298.2961163198068</v>
+        <v>298.3293166654539</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27279,28 +27349,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3571488963376224</v>
+        <v>0.3543773983875732</v>
       </c>
       <c r="J6" t="n">
+        <v>374</v>
+      </c>
+      <c r="K6" t="n">
         <v>373</v>
       </c>
-      <c r="K6" t="n">
-        <v>372</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01191233704349925</v>
+        <v>0.01179194001737938</v>
       </c>
       <c r="M6" t="n">
-        <v>15.23576832349191</v>
+        <v>15.20947341080104</v>
       </c>
       <c r="N6" t="n">
-        <v>581.0244376388433</v>
+        <v>579.5443537023139</v>
       </c>
       <c r="O6" t="n">
-        <v>24.10444850310505</v>
+        <v>24.07372745758982</v>
       </c>
       <c r="P6" t="n">
-        <v>294.6939299439161</v>
+        <v>294.7238765315936</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27357,28 +27427,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2804132687695609</v>
+        <v>-0.28165771717521</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02324966783776206</v>
+        <v>0.02357587077836054</v>
       </c>
       <c r="M7" t="n">
-        <v>10.2131974916615</v>
+        <v>10.19171061907098</v>
       </c>
       <c r="N7" t="n">
-        <v>177.1603754966735</v>
+        <v>176.6979657752038</v>
       </c>
       <c r="O7" t="n">
-        <v>13.31016061122755</v>
+        <v>13.29277870782493</v>
       </c>
       <c r="P7" t="n">
-        <v>323.5920938259948</v>
+        <v>323.6057516560241</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27435,28 +27505,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2048790458369968</v>
+        <v>-0.2054663103321607</v>
       </c>
       <c r="J8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01655684070960106</v>
+        <v>0.01674012625619159</v>
       </c>
       <c r="M8" t="n">
-        <v>8.919930087293006</v>
+        <v>8.899403035639663</v>
       </c>
       <c r="N8" t="n">
-        <v>133.71173869975</v>
+        <v>133.3546949825</v>
       </c>
       <c r="O8" t="n">
-        <v>11.56337920764298</v>
+        <v>11.54793033328916</v>
       </c>
       <c r="P8" t="n">
-        <v>318.1052075596544</v>
+        <v>318.1116527916309</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27513,28 +27583,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2245088667910747</v>
+        <v>-0.2256208037042848</v>
       </c>
       <c r="J9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01918283747933924</v>
+        <v>0.01947219295741598</v>
       </c>
       <c r="M9" t="n">
-        <v>8.756494492549011</v>
+        <v>8.739239957559098</v>
       </c>
       <c r="N9" t="n">
-        <v>139.5377514230362</v>
+        <v>139.1748813487801</v>
       </c>
       <c r="O9" t="n">
-        <v>11.81260984808337</v>
+        <v>11.7972404124346</v>
       </c>
       <c r="P9" t="n">
-        <v>316.028411945678</v>
+        <v>316.0405369747285</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27591,28 +27661,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3445524088652727</v>
+        <v>-0.3424382501003561</v>
       </c>
       <c r="J10" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06056204044086178</v>
+        <v>0.06015052122486908</v>
       </c>
       <c r="M10" t="n">
-        <v>7.692426307459331</v>
+        <v>7.680055533101694</v>
       </c>
       <c r="N10" t="n">
-        <v>98.75994603293999</v>
+        <v>98.53736104302045</v>
       </c>
       <c r="O10" t="n">
-        <v>9.937803883803504</v>
+        <v>9.926598664347242</v>
       </c>
       <c r="P10" t="n">
-        <v>316.3090365534559</v>
+        <v>316.2858336460994</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27669,28 +27739,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1929518976521025</v>
+        <v>-0.1947116820069295</v>
       </c>
       <c r="J11" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K11" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01364137083469497</v>
+        <v>0.01396044558551446</v>
       </c>
       <c r="M11" t="n">
-        <v>9.394360657805789</v>
+        <v>9.380094617194082</v>
       </c>
       <c r="N11" t="n">
-        <v>144.3702134609231</v>
+        <v>144.0112939169294</v>
       </c>
       <c r="O11" t="n">
-        <v>12.01541565909907</v>
+        <v>12.00047057064553</v>
       </c>
       <c r="P11" t="n">
-        <v>313.7484069418372</v>
+        <v>313.7677205875436</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27747,28 +27817,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2197471417758078</v>
+        <v>-0.2224878838222031</v>
       </c>
       <c r="J12" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K12" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01165923099401889</v>
+        <v>0.01200947082404435</v>
       </c>
       <c r="M12" t="n">
-        <v>10.85178574152492</v>
+        <v>10.83951076342358</v>
       </c>
       <c r="N12" t="n">
-        <v>219.5259831185376</v>
+        <v>219.0075665686325</v>
       </c>
       <c r="O12" t="n">
-        <v>14.81640925185781</v>
+        <v>14.79890423540312</v>
       </c>
       <c r="P12" t="n">
-        <v>310.6694103057783</v>
+        <v>310.6994899690684</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27825,28 +27895,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2012151484900856</v>
+        <v>-0.1964684135532708</v>
       </c>
       <c r="J13" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K13" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007934122117834175</v>
+        <v>0.007602260936463212</v>
       </c>
       <c r="M13" t="n">
-        <v>12.38049004155542</v>
+        <v>12.36476041136565</v>
       </c>
       <c r="N13" t="n">
-        <v>271.4973755670571</v>
+        <v>270.985435548215</v>
       </c>
       <c r="O13" t="n">
-        <v>16.47717741505071</v>
+        <v>16.46163526349114</v>
       </c>
       <c r="P13" t="n">
-        <v>320.9023411601555</v>
+        <v>320.8502457107443</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27903,28 +27973,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05258031986615908</v>
+        <v>0.05355621304833046</v>
       </c>
       <c r="J14" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K14" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001190714961849304</v>
+        <v>0.001241971330090408</v>
       </c>
       <c r="M14" t="n">
-        <v>8.347102338666589</v>
+        <v>8.327841344289913</v>
       </c>
       <c r="N14" t="n">
-        <v>124.7820554150026</v>
+        <v>124.4532227202252</v>
       </c>
       <c r="O14" t="n">
-        <v>11.17058885712846</v>
+        <v>11.15586046525436</v>
       </c>
       <c r="P14" t="n">
-        <v>327.6999358435943</v>
+        <v>327.6892345481924</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27981,28 +28051,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2606134553519311</v>
+        <v>0.2604968924999018</v>
       </c>
       <c r="J15" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K15" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03429635221876537</v>
+        <v>0.03444914126742593</v>
       </c>
       <c r="M15" t="n">
-        <v>7.775107840204655</v>
+        <v>7.754812755954427</v>
       </c>
       <c r="N15" t="n">
-        <v>102.8362445543126</v>
+        <v>102.5584416157303</v>
       </c>
       <c r="O15" t="n">
-        <v>10.14082070417935</v>
+        <v>10.12711418004805</v>
       </c>
       <c r="P15" t="n">
-        <v>325.234870540516</v>
+        <v>325.2361480713151</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28059,28 +28129,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1869558900672928</v>
+        <v>0.186591465018014</v>
       </c>
       <c r="J16" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K16" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L16" t="n">
-        <v>0.015240175281376</v>
+        <v>0.01526420360775327</v>
       </c>
       <c r="M16" t="n">
-        <v>8.502071284105323</v>
+        <v>8.480888270029844</v>
       </c>
       <c r="N16" t="n">
-        <v>119.8366966878405</v>
+        <v>119.5132142900186</v>
       </c>
       <c r="O16" t="n">
-        <v>10.94699487018426</v>
+        <v>10.93220994538701</v>
       </c>
       <c r="P16" t="n">
-        <v>329.1950655511783</v>
+        <v>329.1990976561878</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28137,28 +28207,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1091800327754759</v>
+        <v>0.111444306669826</v>
       </c>
       <c r="J17" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K17" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005156612623348766</v>
+        <v>0.005398488473558949</v>
       </c>
       <c r="M17" t="n">
-        <v>8.73315824457339</v>
+        <v>8.721720664196626</v>
       </c>
       <c r="N17" t="n">
-        <v>125.7371823971255</v>
+        <v>125.450712885278</v>
       </c>
       <c r="O17" t="n">
-        <v>11.21325922277397</v>
+        <v>11.20047824359647</v>
       </c>
       <c r="P17" t="n">
-        <v>336.7852625539325</v>
+        <v>336.7607077241653</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28196,7 +28266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R374"/>
+  <dimension ref="A1:R375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62431,6 +62501,98 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-38.224553772672,174.71332347931997</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-38.223916719192594,174.71382501373162</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-38.22326165386615,174.71421999951676</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-38.22258344435509,174.71447806247</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-38.22188503527683,174.71461662815034</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-38.22111768621664,174.71465908792166</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-38.22035709930605,174.71464890589996</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-38.219645473586944,174.71463131424636</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-38.21894348057636,174.71453562984405</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-38.21823508929399,174.7145447032114</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>-38.217518775342306,174.7145499240473</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>-38.216830988198886,174.71417817567652</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>-38.21613447055147,174.71400882243032</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-38.215433885011805,174.71390046477478</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>-38.214733888248475,174.7137858718036</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>-38.21404371668702,174.71356833725872</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R375"/>
+  <dimension ref="A1:R376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22849,10 +22849,10 @@
         <v>311.19</v>
       </c>
       <c r="K375" t="n">
-        <v>305.26</v>
+        <v>308.3</v>
       </c>
       <c r="L375" t="n">
-        <v>299.6</v>
+        <v>303.97</v>
       </c>
       <c r="M375" t="n">
         <v>324.62</v>
@@ -22872,6 +22872,66 @@
       <c r="R375" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="C376" t="n">
+        <v>320.38</v>
+      </c>
+      <c r="D376" t="n">
+        <v>299.56</v>
+      </c>
+      <c r="E376" t="n">
+        <v>296.41</v>
+      </c>
+      <c r="F376" t="n">
+        <v>306.87</v>
+      </c>
+      <c r="G376" t="n">
+        <v>318.42</v>
+      </c>
+      <c r="H376" t="n">
+        <v>312.9</v>
+      </c>
+      <c r="I376" t="n">
+        <v>311.93</v>
+      </c>
+      <c r="J376" t="n">
+        <v>317.46</v>
+      </c>
+      <c r="K376" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="L376" t="n">
+        <v>309.29</v>
+      </c>
+      <c r="M376" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="N376" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="O376" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="P376" t="n">
+        <v>340.97</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B398"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26869,6 +26929,16 @@
       </c>
       <c r="B398" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -27037,28 +27107,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01863362781693485</v>
+        <v>-0.01844993536822124</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001916865553237557</v>
+        <v>0.0001889588181590574</v>
       </c>
       <c r="M2" t="n">
-        <v>7.845740166348289</v>
+        <v>7.825549296820577</v>
       </c>
       <c r="N2" t="n">
-        <v>98.328055322431</v>
+        <v>98.0647754279605</v>
       </c>
       <c r="O2" t="n">
-        <v>9.916050389264417</v>
+        <v>9.902766049339977</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6534418446271</v>
+        <v>347.6514328614318</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27115,28 +27185,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03446549800370446</v>
+        <v>-0.03230239395135827</v>
       </c>
       <c r="J3" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001313811911151541</v>
+        <v>0.001159498286480654</v>
       </c>
       <c r="M3" t="n">
-        <v>5.375131994746155</v>
+        <v>5.370563004995526</v>
       </c>
       <c r="N3" t="n">
-        <v>49.0255518429943</v>
+        <v>48.94045775003354</v>
       </c>
       <c r="O3" t="n">
-        <v>7.001824893768359</v>
+        <v>6.995745689348173</v>
       </c>
       <c r="P3" t="n">
-        <v>317.1233576268938</v>
+        <v>317.0997004775602</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27193,28 +27263,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3054481021089648</v>
+        <v>-0.3059481006031574</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05287817960968821</v>
+        <v>0.05331808191384702</v>
       </c>
       <c r="M4" t="n">
-        <v>6.671368281653401</v>
+        <v>6.655637989769593</v>
       </c>
       <c r="N4" t="n">
-        <v>89.8714373662806</v>
+        <v>89.63228975080462</v>
       </c>
       <c r="O4" t="n">
-        <v>9.480054713253537</v>
+        <v>9.4674331130885</v>
       </c>
       <c r="P4" t="n">
-        <v>308.6485775810184</v>
+        <v>308.6540811665984</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27271,28 +27341,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03861797079599187</v>
+        <v>0.03711442529405697</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003741902924568885</v>
+        <v>0.0003474765931507084</v>
       </c>
       <c r="M5" t="n">
-        <v>10.30016990422981</v>
+        <v>10.28117756297193</v>
       </c>
       <c r="N5" t="n">
-        <v>220.5771745292095</v>
+        <v>220.0119992664438</v>
       </c>
       <c r="O5" t="n">
-        <v>14.85184077914955</v>
+        <v>14.83280146386527</v>
       </c>
       <c r="P5" t="n">
-        <v>298.3293166654539</v>
+        <v>298.3455427397504</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27349,28 +27419,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3543773983875732</v>
+        <v>0.3557644042609944</v>
       </c>
       <c r="J6" t="n">
+        <v>375</v>
+      </c>
+      <c r="K6" t="n">
         <v>374</v>
       </c>
-      <c r="K6" t="n">
-        <v>373</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01179194001737938</v>
+        <v>0.01194701561202394</v>
       </c>
       <c r="M6" t="n">
-        <v>15.20947341080104</v>
+        <v>15.17594867274988</v>
       </c>
       <c r="N6" t="n">
-        <v>579.5443537023139</v>
+        <v>578.0142326252991</v>
       </c>
       <c r="O6" t="n">
-        <v>24.07372745758982</v>
+        <v>24.04192655810468</v>
       </c>
       <c r="P6" t="n">
-        <v>294.7238765315936</v>
+        <v>294.7088447322809</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27427,28 +27497,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.28165771717521</v>
+        <v>-0.280449601559472</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K7" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02357587077836054</v>
+        <v>0.0235029478860993</v>
       </c>
       <c r="M7" t="n">
-        <v>10.19171061907098</v>
+        <v>10.17083224879253</v>
       </c>
       <c r="N7" t="n">
-        <v>176.6979657752038</v>
+        <v>176.237229724611</v>
       </c>
       <c r="O7" t="n">
-        <v>13.29277870782493</v>
+        <v>13.2754370822437</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6057516560241</v>
+        <v>323.5924536806123</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27505,28 +27575,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2054663103321607</v>
+        <v>-0.2053324379613463</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K8" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01674012625619159</v>
+        <v>0.01680940704957601</v>
       </c>
       <c r="M8" t="n">
-        <v>8.899403035639663</v>
+        <v>8.876051565944884</v>
       </c>
       <c r="N8" t="n">
-        <v>133.3546949825</v>
+        <v>132.9963897003043</v>
       </c>
       <c r="O8" t="n">
-        <v>11.54793033328916</v>
+        <v>11.5324060672656</v>
       </c>
       <c r="P8" t="n">
-        <v>318.1116527916309</v>
+        <v>318.110179231094</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27583,28 +27653,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2256208037042848</v>
+        <v>-0.2246364473813424</v>
       </c>
       <c r="J9" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01947219295741598</v>
+        <v>0.01940868310863619</v>
       </c>
       <c r="M9" t="n">
-        <v>8.739239957559098</v>
+        <v>8.720398728678878</v>
       </c>
       <c r="N9" t="n">
-        <v>139.1748813487801</v>
+        <v>138.8113550406793</v>
       </c>
       <c r="O9" t="n">
-        <v>11.7972404124346</v>
+        <v>11.78182307797394</v>
       </c>
       <c r="P9" t="n">
-        <v>316.0405369747285</v>
+        <v>316.0297713971299</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27661,28 +27731,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3424382501003561</v>
+        <v>-0.3370581772519251</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K10" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06015052122486908</v>
+        <v>0.05852966485508948</v>
       </c>
       <c r="M10" t="n">
-        <v>7.680055533101694</v>
+        <v>7.680472453869692</v>
       </c>
       <c r="N10" t="n">
-        <v>98.53736104302045</v>
+        <v>98.55524517417282</v>
       </c>
       <c r="O10" t="n">
-        <v>9.926598664347242</v>
+        <v>9.927499442164317</v>
       </c>
       <c r="P10" t="n">
-        <v>316.2858336460994</v>
+        <v>316.2266140850573</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27739,28 +27809,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1947116820069295</v>
+        <v>-0.1893289897913653</v>
       </c>
       <c r="J11" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K11" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01396044558551446</v>
+        <v>0.01327119603351468</v>
       </c>
       <c r="M11" t="n">
-        <v>9.380094617194082</v>
+        <v>9.360028064191408</v>
       </c>
       <c r="N11" t="n">
-        <v>144.0112939169294</v>
+        <v>143.7346185747396</v>
       </c>
       <c r="O11" t="n">
-        <v>12.00047057064553</v>
+        <v>11.9889373413468</v>
       </c>
       <c r="P11" t="n">
-        <v>313.7677205875436</v>
+        <v>313.7085234780479</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27817,28 +27887,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2224878838222031</v>
+        <v>-0.2178548003861704</v>
       </c>
       <c r="J12" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K12" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01200947082404435</v>
+        <v>0.01158399221929718</v>
       </c>
       <c r="M12" t="n">
-        <v>10.83951076342358</v>
+        <v>10.80573742269442</v>
       </c>
       <c r="N12" t="n">
-        <v>219.0075665686325</v>
+        <v>218.4012828629308</v>
       </c>
       <c r="O12" t="n">
-        <v>14.79890423540312</v>
+        <v>14.7784059648844</v>
       </c>
       <c r="P12" t="n">
-        <v>310.6994899690684</v>
+        <v>310.6485664421105</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27895,28 +27965,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1964684135532708</v>
+        <v>-0.1890611629684546</v>
       </c>
       <c r="J13" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K13" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007602260936463212</v>
+        <v>0.007068478466156991</v>
       </c>
       <c r="M13" t="n">
-        <v>12.36476041136565</v>
+        <v>12.35877895818811</v>
       </c>
       <c r="N13" t="n">
-        <v>270.985435548215</v>
+        <v>270.7929869278636</v>
       </c>
       <c r="O13" t="n">
-        <v>16.46163526349114</v>
+        <v>16.45578885765929</v>
       </c>
       <c r="P13" t="n">
-        <v>320.8502457107443</v>
+        <v>320.7687125901864</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27973,28 +28043,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05355621304833046</v>
+        <v>0.05734798070850076</v>
       </c>
       <c r="J14" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K14" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001241971330090408</v>
+        <v>0.001430021132764248</v>
       </c>
       <c r="M14" t="n">
-        <v>8.327841344289913</v>
+        <v>8.31824939005708</v>
       </c>
       <c r="N14" t="n">
-        <v>124.4532227202252</v>
+        <v>124.2578761675881</v>
       </c>
       <c r="O14" t="n">
-        <v>11.15586046525436</v>
+        <v>11.14710169360575</v>
       </c>
       <c r="P14" t="n">
-        <v>327.6892345481924</v>
+        <v>327.6475325481208</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28051,28 +28121,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2604968924999018</v>
+        <v>0.2651568937366682</v>
       </c>
       <c r="J15" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K15" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03444914126742593</v>
+        <v>0.03576652026161553</v>
       </c>
       <c r="M15" t="n">
-        <v>7.754812755954427</v>
+        <v>7.753089845471373</v>
       </c>
       <c r="N15" t="n">
-        <v>102.5584416157303</v>
+        <v>102.4945959327172</v>
       </c>
       <c r="O15" t="n">
-        <v>10.12711418004805</v>
+        <v>10.12396147428057</v>
       </c>
       <c r="P15" t="n">
-        <v>325.2361480713151</v>
+        <v>325.1849240168242</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28129,28 +28199,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.186591465018014</v>
+        <v>0.1901759833913451</v>
       </c>
       <c r="J16" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K16" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01526420360775327</v>
+        <v>0.01591700216026037</v>
       </c>
       <c r="M16" t="n">
-        <v>8.480888270029844</v>
+        <v>8.476284359540477</v>
       </c>
       <c r="N16" t="n">
-        <v>119.5132142900186</v>
+        <v>119.3140181585964</v>
       </c>
       <c r="O16" t="n">
-        <v>10.93220994538701</v>
+        <v>10.92309563075396</v>
       </c>
       <c r="P16" t="n">
-        <v>329.1990976561878</v>
+        <v>329.1593218124976</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28207,28 +28277,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.111444306669826</v>
+        <v>0.1170313474465975</v>
       </c>
       <c r="J17" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K17" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005398488473558949</v>
+        <v>0.005967461555880127</v>
       </c>
       <c r="M17" t="n">
-        <v>8.721720664196626</v>
+        <v>8.727777828507207</v>
       </c>
       <c r="N17" t="n">
-        <v>125.450712885278</v>
+        <v>125.4284912476968</v>
       </c>
       <c r="O17" t="n">
-        <v>11.20047824359647</v>
+        <v>11.19948620462996</v>
       </c>
       <c r="P17" t="n">
-        <v>336.7607077241653</v>
+        <v>336.699938004654</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28266,7 +28336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R375"/>
+  <dimension ref="A1:R376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62554,12 +62624,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>-38.21823508929399,174.7145447032114</t>
+          <t>-38.2182372012471,174.71451008783757</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>-38.217518775342306,174.7145499240473</t>
+          <t>-38.21752242604311,174.71450023134324</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -62590,6 +62660,98 @@
       <c r="R375" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-38.22454575170552,174.7132760142424</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-38.22390879275689,174.71377810743851</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-38.22325991762789,174.71420972489028</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-38.222577688393486,174.7144440001573</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-38.22186976783971,174.71452628013083</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-38.22111437393511,174.71460603153236</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-38.22035789956861,174.71463340654427</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>-38.219648259451766,174.7145856529578</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-38.21894783646343,174.71446423493964</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-38.21824245329694,174.7144240048581</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>-38.21752687034628,174.71443973586966</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>-38.21683632043484,174.7141194052677</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>-38.21614032876683,174.71394748637445</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>-38.215443792981624,174.7137967273159</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>-38.2147420094688,174.71370084190232</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>-38.21405077661007,174.71349441860593</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R376"/>
+  <dimension ref="A1:R377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22935,6 +22935,66 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>349.78</v>
+      </c>
+      <c r="C377" t="n">
+        <v>321.69</v>
+      </c>
+      <c r="D377" t="n">
+        <v>311.53</v>
+      </c>
+      <c r="E377" t="n">
+        <v>309.78</v>
+      </c>
+      <c r="F377" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="G377" t="n">
+        <v>328.16</v>
+      </c>
+      <c r="H377" t="n">
+        <v>320.52</v>
+      </c>
+      <c r="I377" t="n">
+        <v>319.31</v>
+      </c>
+      <c r="J377" t="n">
+        <v>327.35</v>
+      </c>
+      <c r="K377" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="L377" t="n">
+        <v>315.32</v>
+      </c>
+      <c r="M377" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="N377" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="O377" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="P377" t="n">
+        <v>350.33</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22946,7 +23006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26939,6 +26999,26 @@
       </c>
       <c r="B399" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -27107,28 +27187,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01844993536822124</v>
+        <v>-0.01708630501163825</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001889588181590574</v>
+        <v>0.0001629365706824482</v>
       </c>
       <c r="M2" t="n">
-        <v>7.825549296820577</v>
+        <v>7.810789605399416</v>
       </c>
       <c r="N2" t="n">
-        <v>98.0647754279605</v>
+        <v>97.82078356975599</v>
       </c>
       <c r="O2" t="n">
-        <v>9.902766049339977</v>
+        <v>9.890438997827951</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6514328614318</v>
+        <v>347.6364322656797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27185,28 +27265,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03230239395135827</v>
+        <v>-0.02946667309210174</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K3" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001159498286480654</v>
+        <v>0.0009688574781754333</v>
       </c>
       <c r="M3" t="n">
-        <v>5.370563004995526</v>
+        <v>5.36901819039578</v>
       </c>
       <c r="N3" t="n">
-        <v>48.94045775003354</v>
+        <v>48.88836445067587</v>
       </c>
       <c r="O3" t="n">
-        <v>6.995745689348173</v>
+        <v>6.9920214852842</v>
       </c>
       <c r="P3" t="n">
-        <v>317.0997004775602</v>
+        <v>317.0685061718083</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27263,28 +27343,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3059481006031574</v>
+        <v>-0.3001451373941096</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05331808191384702</v>
+        <v>0.05151289644498458</v>
       </c>
       <c r="M4" t="n">
-        <v>6.655637989769593</v>
+        <v>6.671994002892768</v>
       </c>
       <c r="N4" t="n">
-        <v>89.63228975080462</v>
+        <v>89.71731367335711</v>
       </c>
       <c r="O4" t="n">
-        <v>9.4674331130885</v>
+        <v>9.471922385311078</v>
       </c>
       <c r="P4" t="n">
-        <v>308.6540811665984</v>
+        <v>308.5898370022048</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27341,28 +27421,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03711442529405697</v>
+        <v>0.04245761852781393</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003474765931507084</v>
+        <v>0.0004565917895995586</v>
       </c>
       <c r="M5" t="n">
-        <v>10.28117756297193</v>
+        <v>10.27929362478507</v>
       </c>
       <c r="N5" t="n">
-        <v>220.0119992664438</v>
+        <v>219.7145292684194</v>
       </c>
       <c r="O5" t="n">
-        <v>14.83280146386527</v>
+        <v>14.82277063400832</v>
       </c>
       <c r="P5" t="n">
-        <v>298.3455427397504</v>
+        <v>298.2875375107553</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27419,28 +27499,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3557644042609944</v>
+        <v>0.363910517046561</v>
       </c>
       <c r="J6" t="n">
+        <v>376</v>
+      </c>
+      <c r="K6" t="n">
         <v>375</v>
       </c>
-      <c r="K6" t="n">
-        <v>374</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01194701561202394</v>
+        <v>0.01254748685564711</v>
       </c>
       <c r="M6" t="n">
-        <v>15.17594867274988</v>
+        <v>15.17738591674125</v>
       </c>
       <c r="N6" t="n">
-        <v>578.0142326252991</v>
+        <v>577.136824327105</v>
       </c>
       <c r="O6" t="n">
-        <v>24.04192655810468</v>
+        <v>24.02367216574321</v>
       </c>
       <c r="P6" t="n">
-        <v>294.7088447322809</v>
+        <v>294.6200382990299</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27497,28 +27577,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.280449601559472</v>
+        <v>-0.2741177196159927</v>
       </c>
       <c r="J7" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K7" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0235029478860993</v>
+        <v>0.02255165647925117</v>
       </c>
       <c r="M7" t="n">
-        <v>10.17083224879253</v>
+        <v>10.17721862757117</v>
       </c>
       <c r="N7" t="n">
-        <v>176.237229724611</v>
+        <v>176.1520758542983</v>
       </c>
       <c r="O7" t="n">
-        <v>13.2754370822437</v>
+        <v>13.27222949825305</v>
       </c>
       <c r="P7" t="n">
-        <v>323.5924536806123</v>
+        <v>323.5223538971321</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27575,28 +27655,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2053324379613463</v>
+        <v>-0.2011827913339146</v>
       </c>
       <c r="J8" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01680940704957601</v>
+        <v>0.01621664453577609</v>
       </c>
       <c r="M8" t="n">
-        <v>8.876051565944884</v>
+        <v>8.869677812227708</v>
       </c>
       <c r="N8" t="n">
-        <v>132.9963897003043</v>
+        <v>132.8061875975433</v>
       </c>
       <c r="O8" t="n">
-        <v>11.5324060672656</v>
+        <v>11.52415669789088</v>
       </c>
       <c r="P8" t="n">
-        <v>318.110179231094</v>
+        <v>318.0642388088469</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27653,28 +27733,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2246364473813424</v>
+        <v>-0.2197989863864017</v>
       </c>
       <c r="J9" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01940868310863619</v>
+        <v>0.01866854982292487</v>
       </c>
       <c r="M9" t="n">
-        <v>8.720398728678878</v>
+        <v>8.719281758581857</v>
       </c>
       <c r="N9" t="n">
-        <v>138.8113550406793</v>
+        <v>138.6694115056879</v>
       </c>
       <c r="O9" t="n">
-        <v>11.78182307797394</v>
+        <v>11.77579770145904</v>
       </c>
       <c r="P9" t="n">
-        <v>316.0297713971299</v>
+        <v>315.976556978353</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27731,28 +27811,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3370581772519251</v>
+        <v>-0.3264881334532719</v>
       </c>
       <c r="J10" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05852966485508948</v>
+        <v>0.05483807292903697</v>
       </c>
       <c r="M10" t="n">
-        <v>7.680472453869692</v>
+        <v>7.70130563157637</v>
       </c>
       <c r="N10" t="n">
-        <v>98.55524517417282</v>
+        <v>99.37039446070847</v>
       </c>
       <c r="O10" t="n">
-        <v>9.927499442164317</v>
+        <v>9.968470016041001</v>
       </c>
       <c r="P10" t="n">
-        <v>316.2266140850573</v>
+        <v>316.109593933975</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27809,28 +27889,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1893289897913653</v>
+        <v>-0.1800412374447952</v>
       </c>
       <c r="J11" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K11" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01327119603351468</v>
+        <v>0.0120137905311638</v>
       </c>
       <c r="M11" t="n">
-        <v>9.360028064191408</v>
+        <v>9.371832499481441</v>
       </c>
       <c r="N11" t="n">
-        <v>143.7346185747396</v>
+        <v>144.1826432815333</v>
       </c>
       <c r="O11" t="n">
-        <v>11.9889373413468</v>
+        <v>12.00760772516879</v>
       </c>
       <c r="P11" t="n">
-        <v>313.7085234780479</v>
+        <v>313.6056994781182</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27887,28 +27967,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2178548003861704</v>
+        <v>-0.2123429933836059</v>
       </c>
       <c r="J12" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K12" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01158399221929718</v>
+        <v>0.0110578536923317</v>
       </c>
       <c r="M12" t="n">
-        <v>10.80573742269442</v>
+        <v>10.79929200403521</v>
       </c>
       <c r="N12" t="n">
-        <v>218.4012828629308</v>
+        <v>218.1092550537706</v>
       </c>
       <c r="O12" t="n">
-        <v>14.7784059648844</v>
+        <v>14.76852243976257</v>
       </c>
       <c r="P12" t="n">
-        <v>310.6485664421105</v>
+        <v>310.5875456459375</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27965,28 +28045,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1890611629684546</v>
+        <v>-0.1782051716203389</v>
       </c>
       <c r="J13" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K13" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007068478466156991</v>
+        <v>0.006293587632323461</v>
       </c>
       <c r="M13" t="n">
-        <v>12.35877895818811</v>
+        <v>12.365068393053</v>
       </c>
       <c r="N13" t="n">
-        <v>270.7929869278636</v>
+        <v>271.2055625063321</v>
       </c>
       <c r="O13" t="n">
-        <v>16.45578885765929</v>
+        <v>16.4683199661147</v>
       </c>
       <c r="P13" t="n">
-        <v>320.7687125901864</v>
+        <v>320.6485267355292</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28043,28 +28123,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05734798070850076</v>
+        <v>0.06322921715301459</v>
       </c>
       <c r="J14" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K14" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001430021132764248</v>
+        <v>0.001742828282670583</v>
       </c>
       <c r="M14" t="n">
-        <v>8.31824939005708</v>
+        <v>8.315608558666121</v>
       </c>
       <c r="N14" t="n">
-        <v>124.2578761675881</v>
+        <v>124.2584269325006</v>
       </c>
       <c r="O14" t="n">
-        <v>11.14710169360575</v>
+        <v>11.14712639797812</v>
       </c>
       <c r="P14" t="n">
-        <v>327.6475325481208</v>
+        <v>327.5824734522613</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28121,28 +28201,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2651568937366682</v>
+        <v>0.2732581468688607</v>
       </c>
       <c r="J15" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K15" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03576652026161553</v>
+        <v>0.03787905894881649</v>
       </c>
       <c r="M15" t="n">
-        <v>7.753089845471373</v>
+        <v>7.765006486419136</v>
       </c>
       <c r="N15" t="n">
-        <v>102.4945959327172</v>
+        <v>102.854475914156</v>
       </c>
       <c r="O15" t="n">
-        <v>10.12396147428057</v>
+        <v>10.14171957382751</v>
       </c>
       <c r="P15" t="n">
-        <v>325.1849240168242</v>
+        <v>325.0953554144569</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28199,28 +28279,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1901759833913451</v>
+        <v>0.1986954540928302</v>
       </c>
       <c r="J16" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K16" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01591700216026037</v>
+        <v>0.01734642741058978</v>
       </c>
       <c r="M16" t="n">
-        <v>8.476284359540477</v>
+        <v>8.496271914574013</v>
       </c>
       <c r="N16" t="n">
-        <v>119.3140181585964</v>
+        <v>119.6839943242105</v>
       </c>
       <c r="O16" t="n">
-        <v>10.92309563075396</v>
+        <v>10.94001802211543</v>
       </c>
       <c r="P16" t="n">
-        <v>329.1593218124976</v>
+        <v>329.0642408417156</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28277,28 +28357,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1170313474465975</v>
+        <v>0.1265106626231582</v>
       </c>
       <c r="J17" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K17" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005967461555880127</v>
+        <v>0.006955265728421312</v>
       </c>
       <c r="M17" t="n">
-        <v>8.727777828507207</v>
+        <v>8.754190783581912</v>
       </c>
       <c r="N17" t="n">
-        <v>125.4284912476968</v>
+        <v>125.9873294820453</v>
       </c>
       <c r="O17" t="n">
-        <v>11.19948620462996</v>
+        <v>11.22440775640503</v>
       </c>
       <c r="P17" t="n">
-        <v>336.699938004654</v>
+        <v>336.5962236794241</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28336,7 +28416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R376"/>
+  <dimension ref="A1:R377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62755,6 +62835,98 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-38.224541467557806,174.71325066231083</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-38.22390632045995,174.71376347714428</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-38.223237327575205,174.71407604310727</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-38.22255245640415,174.71429468443918</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-38.221844856666124,174.7143788644021</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-38.22110745076237,174.71449513686005</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-38.22036238335498,174.71454656455836</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-38.21965338650839,174.71450161795696</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>-38.218954707144746,174.7143516199901</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>-38.2182497407593,174.71430455900634</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>-38.21753190774262,174.7143711667417</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>-38.216843114361076,174.71404452403777</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>-38.21614467097246,174.71390202285824</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>-38.21545097214221,174.7137215601538</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>-38.214752144665944,174.7135947245558</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>-38.21405899508186,174.7134083691111</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R377"/>
+  <dimension ref="A1:R379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22995,6 +22995,126 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="C378" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="D378" t="n">
+        <v>310.97</v>
+      </c>
+      <c r="E378" t="n">
+        <v>310.28</v>
+      </c>
+      <c r="F378" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="G378" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="H378" t="n">
+        <v>321.45</v>
+      </c>
+      <c r="I378" t="n">
+        <v>319.89</v>
+      </c>
+      <c r="J378" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="K378" t="n">
+        <v>326.05</v>
+      </c>
+      <c r="L378" t="n">
+        <v>314.3</v>
+      </c>
+      <c r="M378" t="n">
+        <v>338.82</v>
+      </c>
+      <c r="N378" t="n">
+        <v>341.63</v>
+      </c>
+      <c r="O378" t="n">
+        <v>347.55</v>
+      </c>
+      <c r="P378" t="n">
+        <v>349.81</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>357.53</v>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="C379" t="n">
+        <v>321.38</v>
+      </c>
+      <c r="D379" t="n">
+        <v>312.04</v>
+      </c>
+      <c r="E379" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="F379" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="G379" t="n">
+        <v>327</v>
+      </c>
+      <c r="H379" t="n">
+        <v>322.39</v>
+      </c>
+      <c r="I379" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="J379" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="K379" t="n">
+        <v>326.22</v>
+      </c>
+      <c r="L379" t="n">
+        <v>314.57</v>
+      </c>
+      <c r="M379" t="n">
+        <v>337.63</v>
+      </c>
+      <c r="N379" t="n">
+        <v>341.23</v>
+      </c>
+      <c r="O379" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="P379" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>357.17</v>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23006,7 +23126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27019,6 +27139,36 @@
       </c>
       <c r="B401" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>
@@ -27187,28 +27337,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01708630501163825</v>
+        <v>-0.0126237256502389</v>
       </c>
       <c r="J2" t="n">
+        <v>378</v>
+      </c>
+      <c r="K2" t="n">
         <v>376</v>
       </c>
-      <c r="K2" t="n">
-        <v>374</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001629365706824482</v>
+        <v>8.984190087746313e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.810789605399416</v>
+        <v>7.789920911144564</v>
       </c>
       <c r="N2" t="n">
-        <v>97.82078356975599</v>
+        <v>97.39910157439547</v>
       </c>
       <c r="O2" t="n">
-        <v>9.890438997827951</v>
+        <v>9.869098316178407</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6364322656797</v>
+        <v>347.5872466745979</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27265,28 +27415,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02946667309210174</v>
+        <v>-0.02404071849795598</v>
       </c>
       <c r="J3" t="n">
+        <v>378</v>
+      </c>
+      <c r="K3" t="n">
         <v>376</v>
       </c>
-      <c r="K3" t="n">
-        <v>374</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0009688574781754333</v>
+        <v>0.0006503080895891022</v>
       </c>
       <c r="M3" t="n">
-        <v>5.36901819039578</v>
+        <v>5.365320852430241</v>
       </c>
       <c r="N3" t="n">
-        <v>48.88836445067587</v>
+        <v>48.77429721232237</v>
       </c>
       <c r="O3" t="n">
-        <v>6.9920214852842</v>
+        <v>6.983859764651806</v>
       </c>
       <c r="P3" t="n">
-        <v>317.0685061718083</v>
+        <v>317.0087055360771</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27343,28 +27493,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3001451373941096</v>
+        <v>-0.2887823221167445</v>
       </c>
       <c r="J4" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05151289644498458</v>
+        <v>0.04805303757353274</v>
       </c>
       <c r="M4" t="n">
-        <v>6.671994002892768</v>
+        <v>6.704162108212268</v>
       </c>
       <c r="N4" t="n">
-        <v>89.71731367335711</v>
+        <v>89.87089445840212</v>
       </c>
       <c r="O4" t="n">
-        <v>9.471922385311078</v>
+        <v>9.480026078993777</v>
       </c>
       <c r="P4" t="n">
-        <v>308.5898370022048</v>
+        <v>308.4637947884391</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27421,28 +27571,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04245761852781393</v>
+        <v>0.05458571962034751</v>
       </c>
       <c r="J5" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004565917895995586</v>
+        <v>0.0007601369017170567</v>
       </c>
       <c r="M5" t="n">
-        <v>10.27929362478507</v>
+        <v>10.28222286365413</v>
       </c>
       <c r="N5" t="n">
-        <v>219.7145292684194</v>
+        <v>219.3077906918317</v>
       </c>
       <c r="O5" t="n">
-        <v>14.82277063400832</v>
+        <v>14.80904421938944</v>
       </c>
       <c r="P5" t="n">
-        <v>298.2875375107553</v>
+        <v>298.1556068310042</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27499,28 +27649,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.363910517046561</v>
+        <v>0.3778892551609488</v>
       </c>
       <c r="J6" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K6" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01254748685564711</v>
+        <v>0.01363983184674344</v>
       </c>
       <c r="M6" t="n">
-        <v>15.17738591674125</v>
+        <v>15.16828065006148</v>
       </c>
       <c r="N6" t="n">
-        <v>577.136824327105</v>
+        <v>575.0840168107492</v>
       </c>
       <c r="O6" t="n">
-        <v>24.02367216574321</v>
+        <v>23.9809094241805</v>
       </c>
       <c r="P6" t="n">
-        <v>294.6200382990299</v>
+        <v>294.4673712816393</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27577,28 +27727,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2741177196159927</v>
+        <v>-0.2628873079812262</v>
       </c>
       <c r="J7" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K7" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02255165647925117</v>
+        <v>0.02093378209424435</v>
       </c>
       <c r="M7" t="n">
-        <v>10.17721862757117</v>
+        <v>10.18219209741497</v>
       </c>
       <c r="N7" t="n">
-        <v>176.1520758542983</v>
+        <v>175.8286145296233</v>
       </c>
       <c r="O7" t="n">
-        <v>13.27222949825305</v>
+        <v>13.26003825520965</v>
       </c>
       <c r="P7" t="n">
-        <v>323.5223538971321</v>
+        <v>323.3977863070317</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27655,28 +27805,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2011827913339146</v>
+        <v>-0.191598301265033</v>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K8" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01621664453577609</v>
+        <v>0.01484235778956455</v>
       </c>
       <c r="M8" t="n">
-        <v>8.869677812227708</v>
+        <v>8.862513624830358</v>
       </c>
       <c r="N8" t="n">
-        <v>132.8061875975433</v>
+        <v>132.547668142425</v>
       </c>
       <c r="O8" t="n">
-        <v>11.52415669789088</v>
+        <v>11.51293481882118</v>
       </c>
       <c r="P8" t="n">
-        <v>318.0642388088469</v>
+        <v>317.9579225358564</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27733,28 +27883,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2197989863864017</v>
+        <v>-0.2083961138586112</v>
       </c>
       <c r="J9" t="n">
+        <v>378</v>
+      </c>
+      <c r="K9" t="n">
         <v>376</v>
       </c>
-      <c r="K9" t="n">
-        <v>374</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01866854982292487</v>
+        <v>0.01691816253924217</v>
       </c>
       <c r="M9" t="n">
-        <v>8.719281758581857</v>
+        <v>8.725581903288626</v>
       </c>
       <c r="N9" t="n">
-        <v>138.6694115056879</v>
+        <v>138.5841361974448</v>
       </c>
       <c r="O9" t="n">
-        <v>11.77579770145904</v>
+        <v>11.77217635772778</v>
       </c>
       <c r="P9" t="n">
-        <v>315.976556978353</v>
+        <v>315.8508651775527</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27811,28 +27961,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3264881334532719</v>
+        <v>-0.30594873489698</v>
       </c>
       <c r="J10" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K10" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05483807292903697</v>
+        <v>0.04803995178400755</v>
       </c>
       <c r="M10" t="n">
-        <v>7.70130563157637</v>
+        <v>7.743601428371486</v>
       </c>
       <c r="N10" t="n">
-        <v>99.37039446070847</v>
+        <v>100.9019204115972</v>
       </c>
       <c r="O10" t="n">
-        <v>9.968470016041001</v>
+        <v>10.04499479400548</v>
       </c>
       <c r="P10" t="n">
-        <v>316.109593933975</v>
+        <v>315.8817659636598</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27889,28 +28039,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1800412374447952</v>
+        <v>-0.1620523024689963</v>
       </c>
       <c r="J11" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K11" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0120137905311638</v>
+        <v>0.009756356768971242</v>
       </c>
       <c r="M11" t="n">
-        <v>9.371832499481441</v>
+        <v>9.393400639996448</v>
       </c>
       <c r="N11" t="n">
-        <v>144.1826432815333</v>
+        <v>144.9942403624663</v>
       </c>
       <c r="O11" t="n">
-        <v>12.00760772516879</v>
+        <v>12.04135542048595</v>
       </c>
       <c r="P11" t="n">
-        <v>313.6056994781182</v>
+        <v>313.4061654605543</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27967,28 +28117,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2123429933836059</v>
+        <v>-0.2024586002959657</v>
       </c>
       <c r="J12" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K12" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0110578536923317</v>
+        <v>0.01015128875539117</v>
       </c>
       <c r="M12" t="n">
-        <v>10.79929200403521</v>
+        <v>10.78279164526497</v>
       </c>
       <c r="N12" t="n">
-        <v>218.1092550537706</v>
+        <v>217.4232832118759</v>
       </c>
       <c r="O12" t="n">
-        <v>14.76852243976257</v>
+        <v>14.74528003165338</v>
       </c>
       <c r="P12" t="n">
-        <v>310.5875456459375</v>
+        <v>310.4779065193585</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28045,28 +28195,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1782051716203389</v>
+        <v>-0.1550399737977599</v>
       </c>
       <c r="J13" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K13" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006293587632323461</v>
+        <v>0.004777652437674473</v>
       </c>
       <c r="M13" t="n">
-        <v>12.365068393053</v>
+        <v>12.38345519631891</v>
       </c>
       <c r="N13" t="n">
-        <v>271.2055625063321</v>
+        <v>272.3823035750214</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4683199661147</v>
+        <v>16.50400871228022</v>
       </c>
       <c r="P13" t="n">
-        <v>320.6485267355292</v>
+        <v>320.3915851502323</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28123,28 +28273,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06322921715301459</v>
+        <v>0.07583104352781522</v>
       </c>
       <c r="J14" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K14" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001742828282670583</v>
+        <v>0.002516832062342544</v>
       </c>
       <c r="M14" t="n">
-        <v>8.315608558666121</v>
+        <v>8.313689115204301</v>
       </c>
       <c r="N14" t="n">
-        <v>124.2584269325006</v>
+        <v>124.3711377690542</v>
       </c>
       <c r="O14" t="n">
-        <v>11.14712639797812</v>
+        <v>11.15218085259803</v>
       </c>
       <c r="P14" t="n">
-        <v>327.5824734522613</v>
+        <v>327.4428053914342</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28201,28 +28351,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2732581468688607</v>
+        <v>0.2889582239091631</v>
       </c>
       <c r="J15" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K15" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03787905894881649</v>
+        <v>0.04214200039035332</v>
       </c>
       <c r="M15" t="n">
-        <v>7.765006486419136</v>
+        <v>7.786312253750194</v>
       </c>
       <c r="N15" t="n">
-        <v>102.854475914156</v>
+        <v>103.5109822562279</v>
       </c>
       <c r="O15" t="n">
-        <v>10.14171957382751</v>
+        <v>10.17403470881773</v>
       </c>
       <c r="P15" t="n">
-        <v>325.0953554144569</v>
+        <v>324.9214416055687</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28279,28 +28429,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1986954540928302</v>
+        <v>0.2145538515200414</v>
       </c>
       <c r="J16" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K16" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01734642741058978</v>
+        <v>0.02018718083649595</v>
       </c>
       <c r="M16" t="n">
-        <v>8.496271914574013</v>
+        <v>8.530858942553758</v>
       </c>
       <c r="N16" t="n">
-        <v>119.6839943242105</v>
+        <v>120.2542125018382</v>
       </c>
       <c r="O16" t="n">
-        <v>10.94001802211543</v>
+        <v>10.96604817159938</v>
       </c>
       <c r="P16" t="n">
-        <v>329.0642408417156</v>
+        <v>328.8869224319915</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28357,28 +28507,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1265106626231582</v>
+        <v>0.144220202157754</v>
       </c>
       <c r="J17" t="n">
+        <v>378</v>
+      </c>
+      <c r="K17" t="n">
         <v>376</v>
       </c>
-      <c r="K17" t="n">
-        <v>374</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.006955265728421312</v>
+        <v>0.009006167181601854</v>
       </c>
       <c r="M17" t="n">
-        <v>8.754190783581912</v>
+        <v>8.801442975695682</v>
       </c>
       <c r="N17" t="n">
-        <v>125.9873294820453</v>
+        <v>126.8951299922383</v>
       </c>
       <c r="O17" t="n">
-        <v>11.22440775640503</v>
+        <v>11.264773854465</v>
       </c>
       <c r="P17" t="n">
-        <v>336.5962236794241</v>
+        <v>336.4020875391428</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28416,7 +28566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R377"/>
+  <dimension ref="A1:R379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62927,6 +63077,190 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-38.22453833465332,174.71323212301462</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-38.223906226097434,174.71376291873614</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-38.22323838442323,174.71408229722402</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-38.22255151279573,174.71428910045756</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-38.221844856666124,174.7143788644021</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-38.22110826818559,174.7145082301726</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-38.220362930584365,174.7145359657324</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-38.219653789445275,174.7144950135796</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>-38.21895426253364,174.71435890751033</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>-38.21824953234928,174.7143079749987</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>-38.21753105564853,174.71438276550046</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>-38.216845605455475,174.71401706758286</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>-38.21614602452425,174.713887850938</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>-38.21545078806176,174.71372348751714</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>-38.214751581601945,174.7136006199648</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>-38.214058280434635,174.7134158516767</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-38.224538032686446,174.71323033609457</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-38.223906905507484,174.7137669392749</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-38.22323636508835,174.7140703473939</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-38.2225472099379,174.71426363750317</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-38.22185214131661,174.71442197232517</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-38.221108275293595,174.7145083440275</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-38.22036348369697,174.7145252529404</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-38.21965556792083,174.71446586322335</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>-38.218954908609014,174.71434831783247</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>-38.21824965044831,174.7143060392697</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>-38.217531281202945,174.7143796952408</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>-38.216844380496624,174.71403056889773</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>-38.216145591387864,174.71389238595253</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>-38.21545082054654,174.7137231473942</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>-38.21475101853764,174.71360651537373</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>-38.21405789062686,174.71341993307607</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R379"/>
+  <dimension ref="A1:R381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23115,6 +23115,126 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="C380" t="n">
+        <v>319.34</v>
+      </c>
+      <c r="D380" t="n">
+        <v>313.23</v>
+      </c>
+      <c r="E380" t="n">
+        <v>311.12</v>
+      </c>
+      <c r="F380" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="G380" t="n">
+        <v>327.98</v>
+      </c>
+      <c r="H380" t="n">
+        <v>323.97</v>
+      </c>
+      <c r="I380" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="J380" t="n">
+        <v>331.23</v>
+      </c>
+      <c r="K380" t="n">
+        <v>331.09</v>
+      </c>
+      <c r="L380" t="n">
+        <v>317.78</v>
+      </c>
+      <c r="M380" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="N380" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="O380" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="P380" t="n">
+        <v>351.51</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="C381" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="D381" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="E381" t="n">
+        <v>306.57</v>
+      </c>
+      <c r="F381" t="n">
+        <v>317.96</v>
+      </c>
+      <c r="G381" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="H381" t="n">
+        <v>323.73</v>
+      </c>
+      <c r="I381" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="J381" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="K381" t="n">
+        <v>337.72</v>
+      </c>
+      <c r="L381" t="n">
+        <v>325.15</v>
+      </c>
+      <c r="M381" t="n">
+        <v>341.92</v>
+      </c>
+      <c r="N381" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="O381" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="P381" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23126,7 +23246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B404"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27169,6 +27289,26 @@
       </c>
       <c r="B404" t="n">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -27337,28 +27477,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0126237256502389</v>
+        <v>-0.007499496891259405</v>
       </c>
       <c r="J2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K2" t="n">
         <v>378</v>
       </c>
-      <c r="K2" t="n">
-        <v>376</v>
-      </c>
       <c r="L2" t="n">
-        <v>8.984190087746313e-05</v>
+        <v>3.201502429728276e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.789920911144564</v>
+        <v>7.772339793858403</v>
       </c>
       <c r="N2" t="n">
-        <v>97.39910157439547</v>
+        <v>97.02303307595054</v>
       </c>
       <c r="O2" t="n">
-        <v>9.869098316178407</v>
+        <v>9.850027059655751</v>
       </c>
       <c r="P2" t="n">
-        <v>347.5872466745979</v>
+        <v>347.5305123074702</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27415,28 +27555,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02404071849795598</v>
+        <v>-0.0221405088643405</v>
       </c>
       <c r="J3" t="n">
+        <v>380</v>
+      </c>
+      <c r="K3" t="n">
         <v>378</v>
       </c>
-      <c r="K3" t="n">
-        <v>376</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0006503080895891022</v>
+        <v>0.0005574467205792244</v>
       </c>
       <c r="M3" t="n">
-        <v>5.365320852430241</v>
+        <v>5.345602774241318</v>
       </c>
       <c r="N3" t="n">
-        <v>48.77429721232237</v>
+        <v>48.54091921332757</v>
       </c>
       <c r="O3" t="n">
-        <v>6.983859764651806</v>
+        <v>6.967131347500747</v>
       </c>
       <c r="P3" t="n">
-        <v>317.0087055360771</v>
+        <v>316.9876739698382</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27493,28 +27633,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2887823221167445</v>
+        <v>-0.276537076483741</v>
       </c>
       <c r="J4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04805303757353274</v>
+        <v>0.04436017349177002</v>
       </c>
       <c r="M4" t="n">
-        <v>6.704162108212268</v>
+        <v>6.742054447054457</v>
       </c>
       <c r="N4" t="n">
-        <v>89.87089445840212</v>
+        <v>90.13395167108226</v>
       </c>
       <c r="O4" t="n">
-        <v>9.480026078993777</v>
+        <v>9.493890228514456</v>
       </c>
       <c r="P4" t="n">
-        <v>308.4637947884391</v>
+        <v>308.3273316544892</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27571,28 +27711,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05458571962034751</v>
+        <v>0.0638455934565265</v>
       </c>
       <c r="J5" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007601369017170567</v>
+        <v>0.001048777041719906</v>
       </c>
       <c r="M5" t="n">
-        <v>10.28222286365413</v>
+        <v>10.27191665731237</v>
       </c>
       <c r="N5" t="n">
-        <v>219.3077906918317</v>
+        <v>218.6209881850674</v>
       </c>
       <c r="O5" t="n">
-        <v>14.80904421938944</v>
+        <v>14.78583741913414</v>
       </c>
       <c r="P5" t="n">
-        <v>298.1556068310042</v>
+        <v>298.0544197846595</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27649,28 +27789,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3778892551609488</v>
+        <v>0.3911069683054371</v>
       </c>
       <c r="J6" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K6" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01363983184674344</v>
+        <v>0.014732116691344</v>
       </c>
       <c r="M6" t="n">
-        <v>15.16828065006148</v>
+        <v>15.15481963156553</v>
       </c>
       <c r="N6" t="n">
-        <v>575.0840168107492</v>
+        <v>572.9391297509629</v>
       </c>
       <c r="O6" t="n">
-        <v>23.9809094241805</v>
+        <v>23.93614692783621</v>
       </c>
       <c r="P6" t="n">
-        <v>294.4673712816393</v>
+        <v>294.3222916191783</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27727,28 +27867,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2628873079812262</v>
+        <v>-0.2491133473796667</v>
       </c>
       <c r="J7" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K7" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02093378209424435</v>
+        <v>0.0189426899195233</v>
       </c>
       <c r="M7" t="n">
-        <v>10.18219209741497</v>
+        <v>10.20027729547187</v>
       </c>
       <c r="N7" t="n">
-        <v>175.8286145296233</v>
+        <v>175.8439357406296</v>
       </c>
       <c r="O7" t="n">
-        <v>13.26003825520965</v>
+        <v>13.26061596384684</v>
       </c>
       <c r="P7" t="n">
-        <v>323.3977863070317</v>
+        <v>323.2442602132607</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27805,28 +27945,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.191598301265033</v>
+        <v>-0.1802130978914779</v>
       </c>
       <c r="J8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K8" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01484235778956455</v>
+        <v>0.01323458029275904</v>
       </c>
       <c r="M8" t="n">
-        <v>8.862513624830358</v>
+        <v>8.863727449144763</v>
       </c>
       <c r="N8" t="n">
-        <v>132.547668142425</v>
+        <v>132.4820762874086</v>
       </c>
       <c r="O8" t="n">
-        <v>11.51293481882118</v>
+        <v>11.51008585056639</v>
       </c>
       <c r="P8" t="n">
-        <v>317.9579225358564</v>
+        <v>317.8310385223839</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27883,28 +28023,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2083961138586112</v>
+        <v>-0.1897348360546049</v>
       </c>
       <c r="J9" t="n">
+        <v>380</v>
+      </c>
+      <c r="K9" t="n">
         <v>378</v>
       </c>
-      <c r="K9" t="n">
-        <v>376</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01691816253924217</v>
+        <v>0.01403861389379779</v>
       </c>
       <c r="M9" t="n">
-        <v>8.725581903288626</v>
+        <v>8.766958003511414</v>
       </c>
       <c r="N9" t="n">
-        <v>138.5841361974448</v>
+        <v>139.6394591113744</v>
       </c>
       <c r="O9" t="n">
-        <v>11.77217635772778</v>
+        <v>11.81691411119563</v>
       </c>
       <c r="P9" t="n">
-        <v>315.8508651775527</v>
+        <v>315.6441676072116</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27961,28 +28101,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.30594873489698</v>
+        <v>-0.2798718740312132</v>
       </c>
       <c r="J10" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K10" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04803995178400755</v>
+        <v>0.0396761918450762</v>
       </c>
       <c r="M10" t="n">
-        <v>7.743601428371486</v>
+        <v>7.809441095293547</v>
       </c>
       <c r="N10" t="n">
-        <v>100.9019204115972</v>
+        <v>103.725825253593</v>
       </c>
       <c r="O10" t="n">
-        <v>10.04499479400548</v>
+        <v>10.18458763296742</v>
       </c>
       <c r="P10" t="n">
-        <v>315.8817659636598</v>
+        <v>315.59112688589</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28039,28 +28179,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1620523024689963</v>
+        <v>-0.1359199781610686</v>
       </c>
       <c r="J11" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K11" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009756356768971242</v>
+        <v>0.00679954444414832</v>
       </c>
       <c r="M11" t="n">
-        <v>9.393400639996448</v>
+        <v>9.449824673983704</v>
       </c>
       <c r="N11" t="n">
-        <v>144.9942403624663</v>
+        <v>147.6401093233859</v>
       </c>
       <c r="O11" t="n">
-        <v>12.04135542048595</v>
+        <v>12.15072464190453</v>
       </c>
       <c r="P11" t="n">
-        <v>313.4061654605543</v>
+        <v>313.1148909022636</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28117,28 +28257,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2024586002959657</v>
+        <v>-0.1855165789734581</v>
       </c>
       <c r="J12" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K12" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01015128875539117</v>
+        <v>0.008573218732523702</v>
       </c>
       <c r="M12" t="n">
-        <v>10.78279164526497</v>
+        <v>10.79794637011535</v>
       </c>
       <c r="N12" t="n">
-        <v>217.4232832118759</v>
+        <v>217.7523591405046</v>
       </c>
       <c r="O12" t="n">
-        <v>14.74528003165338</v>
+        <v>14.75643449958372</v>
       </c>
       <c r="P12" t="n">
-        <v>310.4779065193585</v>
+        <v>310.2890515466651</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28195,28 +28335,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1550399737977599</v>
+        <v>-0.1300512758870407</v>
       </c>
       <c r="J13" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K13" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004777652437674473</v>
+        <v>0.003365624049733618</v>
       </c>
       <c r="M13" t="n">
-        <v>12.38345519631891</v>
+        <v>12.40764584230765</v>
       </c>
       <c r="N13" t="n">
-        <v>272.3823035750214</v>
+        <v>274.0186785671769</v>
       </c>
       <c r="O13" t="n">
-        <v>16.50400871228022</v>
+        <v>16.55350955438686</v>
       </c>
       <c r="P13" t="n">
-        <v>320.3915851502323</v>
+        <v>320.1130764390716</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28273,28 +28413,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07583104352781522</v>
+        <v>0.08487009919413489</v>
       </c>
       <c r="J14" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K14" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002516832062342544</v>
+        <v>0.00317452629987458</v>
       </c>
       <c r="M14" t="n">
-        <v>8.313689115204301</v>
+        <v>8.300330431773716</v>
       </c>
       <c r="N14" t="n">
-        <v>124.3711377690542</v>
+        <v>124.1373930988654</v>
       </c>
       <c r="O14" t="n">
-        <v>11.15218085259803</v>
+        <v>11.14169614999734</v>
       </c>
       <c r="P14" t="n">
-        <v>327.4428053914342</v>
+        <v>327.3421668319184</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28351,28 +28491,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2889582239091631</v>
+        <v>0.3004212579389687</v>
       </c>
       <c r="J15" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K15" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04214200039035332</v>
+        <v>0.04557702505425565</v>
       </c>
       <c r="M15" t="n">
-        <v>7.786312253750194</v>
+        <v>7.791572693318404</v>
       </c>
       <c r="N15" t="n">
-        <v>103.5109822562279</v>
+        <v>103.6757647857416</v>
       </c>
       <c r="O15" t="n">
-        <v>10.17403470881773</v>
+        <v>10.18212967830117</v>
       </c>
       <c r="P15" t="n">
-        <v>324.9214416055687</v>
+        <v>324.7938953979756</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28429,28 +28569,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2145538515200414</v>
+        <v>0.2302843393775278</v>
       </c>
       <c r="J16" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K16" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02018718083649595</v>
+        <v>0.02320687066212335</v>
       </c>
       <c r="M16" t="n">
-        <v>8.530858942553758</v>
+        <v>8.563714654998655</v>
       </c>
       <c r="N16" t="n">
-        <v>120.2542125018382</v>
+        <v>120.8294275103662</v>
       </c>
       <c r="O16" t="n">
-        <v>10.96604817159938</v>
+        <v>10.99224397065341</v>
       </c>
       <c r="P16" t="n">
-        <v>328.8869224319915</v>
+        <v>328.7102185334364</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28507,28 +28647,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.144220202157754</v>
+        <v>0.1646731702110052</v>
       </c>
       <c r="J17" t="n">
+        <v>380</v>
+      </c>
+      <c r="K17" t="n">
         <v>378</v>
       </c>
-      <c r="K17" t="n">
-        <v>376</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.009006167181601854</v>
+        <v>0.01164395215918224</v>
       </c>
       <c r="M17" t="n">
-        <v>8.801442975695682</v>
+        <v>8.863480955257668</v>
       </c>
       <c r="N17" t="n">
-        <v>126.8951299922383</v>
+        <v>128.3429039512996</v>
       </c>
       <c r="O17" t="n">
-        <v>11.264773854465</v>
+        <v>11.3288527199933</v>
       </c>
       <c r="P17" t="n">
-        <v>336.4020875391428</v>
+        <v>336.1767834842469</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28566,7 +28706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R379"/>
+  <dimension ref="A1:R381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63261,6 +63401,190 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-38.22453442795499,174.71320900473768</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-38.22391075549511,174.71378972232927</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-38.22323411928454,174.71405705739662</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-38.22254992753297,174.71427971936876</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-38.22184970681085,174.71440756579042</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-38.22110757870697,174.71449718624808</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>-38.220364413394684,174.7145072463321</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>-38.21965756175009,174.7144331829391</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>-38.21895740258995,174.7143074393963</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>-38.218253033624414,174.71425058632425</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>-38.21753396278839,174.71434319326346</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>-38.21684581133075,174.7140147984543</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>-38.2161447467714,174.71390122923071</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>-38.21545059315302,174.71372552825477</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>-38.214753422387034,174.7135813465119</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>-38.21406105239702,174.71338682839092</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-38.22453912731617,174.71323681367977</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-38.22391498292735,174.713814739019</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-38.22323659155586,174.71407168756173</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-38.22255851436381,174.7143305336043</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-38.22184883869208,174.71440242857668</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-38.221105147753434,174.7144582478763</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-38.22036427217497,174.71450998151315</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-38.21966197315196,174.71436087637935</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>-38.218959799299206,174.7142681551022</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-38.21825763942593,174.7141750928794</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>-38.21754011953214,174.71425938653118</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>-38.216848796517475,174.71398189608797</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>-38.21613999308437,174.7139510010101</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>-38.215442926714665,174.7138057972589</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>-38.21474970832919,174.71362023353637</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>-38.21406185366608,174.71337843884692</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
